--- a/artfynd/A 60460-2022 artfynd.xlsx
+++ b/artfynd/A 60460-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122744329</v>
+        <v>122744328</v>
       </c>
       <c r="B2" t="n">
-        <v>90890</v>
+        <v>90993</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583100</v>
+        <v>583107</v>
       </c>
       <c r="R2" t="n">
         <v>6510809</v>
@@ -785,7 +785,7 @@
         <v>122744331</v>
       </c>
       <c r="B3" t="n">
-        <v>100510</v>
+        <v>100613</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122744328</v>
+        <v>122744329</v>
       </c>
       <c r="B4" t="n">
-        <v>90890</v>
+        <v>90993</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583107</v>
+        <v>583100</v>
       </c>
       <c r="R4" t="n">
         <v>6510809</v>

--- a/artfynd/A 60460-2022 artfynd.xlsx
+++ b/artfynd/A 60460-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744328</v>
       </c>
       <c r="B2" t="n">
-        <v>90993</v>
+        <v>90997</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122744331</v>
+        <v>122744329</v>
       </c>
       <c r="B3" t="n">
-        <v>100613</v>
+        <v>90997</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>5321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583070</v>
+        <v>583100</v>
       </c>
       <c r="R3" t="n">
-        <v>6510842</v>
+        <v>6510809</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,6 +866,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -888,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122744329</v>
+        <v>122744331</v>
       </c>
       <c r="B4" t="n">
-        <v>90993</v>
+        <v>100621</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5321</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583100</v>
+        <v>583070</v>
       </c>
       <c r="R4" t="n">
-        <v>6510809</v>
+        <v>6510842</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,7 +973,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 60460-2022 artfynd.xlsx
+++ b/artfynd/A 60460-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122744328</v>
+        <v>122744329</v>
       </c>
       <c r="B2" t="n">
         <v>90997</v>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583107</v>
+        <v>583100</v>
       </c>
       <c r="R2" t="n">
         <v>6510809</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122744329</v>
+        <v>122744331</v>
       </c>
       <c r="B3" t="n">
-        <v>90997</v>
+        <v>100621</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5321</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583100</v>
+        <v>583070</v>
       </c>
       <c r="R3" t="n">
-        <v>6510809</v>
+        <v>6510842</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +866,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -889,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122744331</v>
+        <v>122744328</v>
       </c>
       <c r="B4" t="n">
-        <v>100621</v>
+        <v>90997</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>5321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583070</v>
+        <v>583107</v>
       </c>
       <c r="R4" t="n">
-        <v>6510842</v>
+        <v>6510809</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,6 +972,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 60460-2022 artfynd.xlsx
+++ b/artfynd/A 60460-2022 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>122744331</v>
       </c>
       <c r="B3" t="n">
-        <v>100621</v>
+        <v>100623</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 60460-2022 artfynd.xlsx
+++ b/artfynd/A 60460-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122744329</v>
+        <v>122744331</v>
       </c>
       <c r="B2" t="n">
-        <v>90997</v>
+        <v>100623</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5321</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583100</v>
+        <v>583070</v>
       </c>
       <c r="R2" t="n">
-        <v>6510809</v>
+        <v>6510842</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122744331</v>
+        <v>122744328</v>
       </c>
       <c r="B3" t="n">
-        <v>100623</v>
+        <v>90997</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>5321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583070</v>
+        <v>583107</v>
       </c>
       <c r="R3" t="n">
-        <v>6510842</v>
+        <v>6510809</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,6 +865,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -888,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122744328</v>
+        <v>122744329</v>
       </c>
       <c r="B4" t="n">
         <v>90997</v>
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583107</v>
+        <v>583100</v>
       </c>
       <c r="R4" t="n">
         <v>6510809</v>

--- a/artfynd/A 60460-2022 artfynd.xlsx
+++ b/artfynd/A 60460-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122744331</v>
+        <v>122744328</v>
       </c>
       <c r="B2" t="n">
-        <v>100623</v>
+        <v>91005</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>5321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583070</v>
+        <v>583107</v>
       </c>
       <c r="R2" t="n">
-        <v>6510842</v>
+        <v>6510809</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,6 +759,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122744328</v>
+        <v>122744329</v>
       </c>
       <c r="B3" t="n">
-        <v>90997</v>
+        <v>91005</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,7 +822,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583107</v>
+        <v>583100</v>
       </c>
       <c r="R3" t="n">
         <v>6510809</v>
@@ -888,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122744329</v>
+        <v>122744331</v>
       </c>
       <c r="B4" t="n">
-        <v>90997</v>
+        <v>100631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5321</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583100</v>
+        <v>583070</v>
       </c>
       <c r="R4" t="n">
-        <v>6510809</v>
+        <v>6510842</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,7 +973,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 60460-2022 artfynd.xlsx
+++ b/artfynd/A 60460-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122744328</v>
+        <v>122744331</v>
       </c>
       <c r="B2" t="n">
-        <v>91005</v>
+        <v>100631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5321</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583107</v>
+        <v>583070</v>
       </c>
       <c r="R2" t="n">
-        <v>6510809</v>
+        <v>6510842</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -889,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122744331</v>
+        <v>122744328</v>
       </c>
       <c r="B4" t="n">
-        <v>100631</v>
+        <v>91005</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>5321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583070</v>
+        <v>583107</v>
       </c>
       <c r="R4" t="n">
-        <v>6510842</v>
+        <v>6510809</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,6 +972,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 60460-2022 artfynd.xlsx
+++ b/artfynd/A 60460-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122744331</v>
+        <v>122744329</v>
       </c>
       <c r="B2" t="n">
-        <v>100631</v>
+        <v>91005</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>5321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583070</v>
+        <v>583100</v>
       </c>
       <c r="R2" t="n">
-        <v>6510842</v>
+        <v>6510809</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,6 +759,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122744329</v>
+        <v>122744328</v>
       </c>
       <c r="B3" t="n">
         <v>91005</v>
@@ -821,7 +822,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583100</v>
+        <v>583107</v>
       </c>
       <c r="R3" t="n">
         <v>6510809</v>
@@ -888,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122744328</v>
+        <v>122744331</v>
       </c>
       <c r="B4" t="n">
-        <v>91005</v>
+        <v>100631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5321</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583107</v>
+        <v>583070</v>
       </c>
       <c r="R4" t="n">
-        <v>6510809</v>
+        <v>6510842</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,7 +973,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 60460-2022 artfynd.xlsx
+++ b/artfynd/A 60460-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122744329</v>
+        <v>122744331</v>
       </c>
       <c r="B2" t="n">
-        <v>91005</v>
+        <v>100634</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5321</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583100</v>
+        <v>583070</v>
       </c>
       <c r="R2" t="n">
-        <v>6510809</v>
+        <v>6510842</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,7 +784,7 @@
         <v>122744328</v>
       </c>
       <c r="B3" t="n">
-        <v>91005</v>
+        <v>91008</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -889,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122744331</v>
+        <v>122744329</v>
       </c>
       <c r="B4" t="n">
-        <v>100631</v>
+        <v>91008</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>5321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583070</v>
+        <v>583100</v>
       </c>
       <c r="R4" t="n">
-        <v>6510842</v>
+        <v>6510809</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,6 +972,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 60460-2022 artfynd.xlsx
+++ b/artfynd/A 60460-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122744331</v>
+        <v>122744329</v>
       </c>
       <c r="B2" t="n">
-        <v>100634</v>
+        <v>91010</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>5321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583070</v>
+        <v>583100</v>
       </c>
       <c r="R2" t="n">
-        <v>6510842</v>
+        <v>6510809</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,6 +759,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -784,7 +785,7 @@
         <v>122744328</v>
       </c>
       <c r="B3" t="n">
-        <v>91008</v>
+        <v>91010</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -888,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122744329</v>
+        <v>122744331</v>
       </c>
       <c r="B4" t="n">
-        <v>91008</v>
+        <v>100636</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5321</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583100</v>
+        <v>583070</v>
       </c>
       <c r="R4" t="n">
-        <v>6510809</v>
+        <v>6510842</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,7 +973,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 60460-2022 artfynd.xlsx
+++ b/artfynd/A 60460-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744329</v>
       </c>
       <c r="B2" t="n">
-        <v>91946</v>
+        <v>91949</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>122744328</v>
       </c>
       <c r="B3" t="n">
-        <v>91946</v>
+        <v>91949</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>122744331</v>
       </c>
       <c r="B4" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60460-2022 artfynd.xlsx
+++ b/artfynd/A 60460-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744329</v>
       </c>
       <c r="B2" t="n">
-        <v>91949</v>
+        <v>91955</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>122744328</v>
       </c>
       <c r="B3" t="n">
-        <v>91949</v>
+        <v>91955</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>122744331</v>
       </c>
       <c r="B4" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60460-2022 artfynd.xlsx
+++ b/artfynd/A 60460-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744329</v>
       </c>
       <c r="B2" t="n">
-        <v>91955</v>
+        <v>91965</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>122744328</v>
       </c>
       <c r="B3" t="n">
-        <v>91955</v>
+        <v>91965</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>122744331</v>
       </c>
       <c r="B4" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60460-2022 artfynd.xlsx
+++ b/artfynd/A 60460-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744329</v>
       </c>
       <c r="B2" t="n">
-        <v>91965</v>
+        <v>91966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>122744328</v>
       </c>
       <c r="B3" t="n">
-        <v>91965</v>
+        <v>91966</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>122744331</v>
       </c>
       <c r="B4" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60460-2022 artfynd.xlsx
+++ b/artfynd/A 60460-2022 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>122744331</v>
       </c>
       <c r="B4" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60460-2022 artfynd.xlsx
+++ b/artfynd/A 60460-2022 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>122744331</v>
       </c>
       <c r="B4" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60460-2022 artfynd.xlsx
+++ b/artfynd/A 60460-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744329</v>
       </c>
       <c r="B2" t="n">
-        <v>91966</v>
+        <v>91967</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>122744328</v>
       </c>
       <c r="B3" t="n">
-        <v>91966</v>
+        <v>91967</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>122744331</v>
       </c>
       <c r="B4" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60460-2022 artfynd.xlsx
+++ b/artfynd/A 60460-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744329</v>
       </c>
       <c r="B2" t="n">
-        <v>91967</v>
+        <v>91969</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>122744328</v>
       </c>
       <c r="B3" t="n">
-        <v>91967</v>
+        <v>91969</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>122744331</v>
       </c>
       <c r="B4" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60460-2022 artfynd.xlsx
+++ b/artfynd/A 60460-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744329</v>
       </c>
       <c r="B2" t="n">
-        <v>91969</v>
+        <v>91970</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>122744328</v>
       </c>
       <c r="B3" t="n">
-        <v>91969</v>
+        <v>91970</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>122744331</v>
       </c>
       <c r="B4" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60460-2022 artfynd.xlsx
+++ b/artfynd/A 60460-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122744329</v>
+        <v>122744328</v>
       </c>
       <c r="B2" t="n">
-        <v>91974</v>
+        <v>92031</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583100</v>
+        <v>583107</v>
       </c>
       <c r="R2" t="n">
         <v>6510809</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122744328</v>
+        <v>122744329</v>
       </c>
       <c r="B3" t="n">
-        <v>91974</v>
+        <v>92031</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583107</v>
+        <v>583100</v>
       </c>
       <c r="R3" t="n">
         <v>6510809</v>
@@ -882,7 +882,7 @@
         <v>122744331</v>
       </c>
       <c r="B4" t="n">
-        <v>101334</v>
+        <v>101403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60460-2022 artfynd.xlsx
+++ b/artfynd/A 60460-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122744328</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122744329</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,8 +992,18 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122744331</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>